--- a/artfynd/A 12324-2025 artfynd.xlsx
+++ b/artfynd/A 12324-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>106409331</v>
       </c>
       <c r="B2" t="n">
-        <v>107967</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712692.752717764</v>
+        <v>712693</v>
       </c>
       <c r="R2" t="n">
-        <v>6347112.876839684</v>
+        <v>6347113</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>1991-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1991-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 12324-2025 artfynd.xlsx
+++ b/artfynd/A 12324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106409331</v>
       </c>
       <c r="B2" t="n">
-        <v>110439</v>
+        <v>110448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12324-2025 artfynd.xlsx
+++ b/artfynd/A 12324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106409331</v>
       </c>
       <c r="B2" t="n">
-        <v>110448</v>
+        <v>110461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12324-2025 artfynd.xlsx
+++ b/artfynd/A 12324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106409331</v>
       </c>
       <c r="B2" t="n">
-        <v>110461</v>
+        <v>110470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12324-2025 artfynd.xlsx
+++ b/artfynd/A 12324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106409331</v>
       </c>
       <c r="B2" t="n">
-        <v>110470</v>
+        <v>110475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12324-2025 artfynd.xlsx
+++ b/artfynd/A 12324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106409331</v>
       </c>
       <c r="B2" t="n">
-        <v>110475</v>
+        <v>110503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12324-2025 artfynd.xlsx
+++ b/artfynd/A 12324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106409331</v>
       </c>
       <c r="B2" t="n">
-        <v>110503</v>
+        <v>110509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12324-2025 artfynd.xlsx
+++ b/artfynd/A 12324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106409331</v>
       </c>
       <c r="B2" t="n">
-        <v>110509</v>
+        <v>110516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12324-2025 artfynd.xlsx
+++ b/artfynd/A 12324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106409331</v>
       </c>
       <c r="B2" t="n">
-        <v>110516</v>
+        <v>110520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12324-2025 artfynd.xlsx
+++ b/artfynd/A 12324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106409331</v>
       </c>
       <c r="B2" t="n">
-        <v>110520</v>
+        <v>110528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12324-2025 artfynd.xlsx
+++ b/artfynd/A 12324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106409331</v>
       </c>
       <c r="B2" t="n">
-        <v>110531</v>
+        <v>110536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12324-2025 artfynd.xlsx
+++ b/artfynd/A 12324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106409331</v>
       </c>
       <c r="B2" t="n">
-        <v>110536</v>
+        <v>110544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
